--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_44.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_44.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>HoursSleep</t>
+          <t>DV</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>RiskTaking</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.5584429252406889</v>
+        <v>-0.5586554909443583</v>
       </c>
       <c r="C2">
-        <v>-1.645214421193431</v>
+        <v>-0.2230519626684836</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.5258718392829116</v>
+        <v>0.9359596059722601</v>
       </c>
       <c r="C3">
-        <v>-0.1509885428943872</v>
+        <v>0.2339836237003173</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>2.100638418676617</v>
+        <v>-0.2687818031051933</v>
       </c>
       <c r="C4">
-        <v>0.8248707793332467</v>
+        <v>0.06136298886539761</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.2842017824259811</v>
+        <v>0.8384883256966965</v>
       </c>
       <c r="C5">
-        <v>0.1058631954328396</v>
+        <v>-0.4308744120213471</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.07724321464688622</v>
+        <v>0.6891430830762807</v>
       </c>
       <c r="C6">
-        <v>-1.590902979481864</v>
+        <v>-1.878519049322719</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.8328867799910353</v>
+        <v>0.1707484562132414</v>
       </c>
       <c r="C7">
-        <v>-2.055124065902867</v>
+        <v>-0.6186636754169232</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-1.421783997490232</v>
+        <v>1.567594318863287</v>
       </c>
       <c r="C8">
-        <v>-0.2273219524352358</v>
+        <v>-0.08143276858658799</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-1.160507895248583</v>
+        <v>1.139480774491587</v>
       </c>
       <c r="C9">
-        <v>0.5736404402130763</v>
+        <v>-1.415819303870972</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-2.012600954254181</v>
+        <v>-2.113588561466682</v>
       </c>
       <c r="C10">
-        <v>1.129055908289418</v>
+        <v>1.072440172890308</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-1.836339373755227</v>
+        <v>-0.8425369356064735</v>
       </c>
       <c r="C11">
-        <v>-0.5054033140953526</v>
+        <v>-1.113685879757267</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.1548033099804749</v>
+        <v>0.4669221062633801</v>
       </c>
       <c r="C12">
-        <v>0.1537603959323662</v>
+        <v>0.4793786064426327</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.6920793983596789</v>
+        <v>0.6627816332618984</v>
       </c>
       <c r="C13">
-        <v>0.5522211137579467</v>
+        <v>0.7168232233659013</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.3945841281168991</v>
+        <v>-0.5319468467512514</v>
       </c>
       <c r="C14">
-        <v>0.5712163522510582</v>
+        <v>-0.2707759259470245</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.7668708627101386</v>
+        <v>0.4963653188058614</v>
       </c>
       <c r="C15">
-        <v>0.6090422878096656</v>
+        <v>-0.0408076644117579</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.507581034424538</v>
+        <v>-0.6700400359372738</v>
       </c>
       <c r="C16">
-        <v>1.4771656296122</v>
+        <v>0.5444163891610443</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-1.198260100914431</v>
+        <v>1.67684867638654</v>
       </c>
       <c r="C17">
-        <v>0.42718303910828</v>
+        <v>-2.297392597792338</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.1367299484620717</v>
+        <v>0.7616400208499715</v>
       </c>
       <c r="C18">
-        <v>0.6946210049894923</v>
+        <v>-1.803129928118628</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>2.120832163661802</v>
+        <v>-1.611922046961829</v>
       </c>
       <c r="C19">
-        <v>0.287941156719062</v>
+        <v>0.1894303338837466</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.3858582495517314</v>
+        <v>-0.4489456222777802</v>
       </c>
       <c r="C20">
-        <v>-0.03000263995100737</v>
+        <v>0.09083505743015832</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.06285529796470285</v>
+        <v>-1.519495285543742</v>
       </c>
       <c r="C21">
-        <v>0.04895469575894588</v>
+        <v>-0.01485835768699817</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.3039962615841835</v>
+        <v>0.02758462397852849</v>
       </c>
       <c r="C22">
-        <v>-0.4636862649663581</v>
+        <v>-0.6518410010978738</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.8463540734811649</v>
+        <v>-0.9892191206957814</v>
       </c>
       <c r="C23">
-        <v>0.1566225356354665</v>
+        <v>0.5614459213321178</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.734396097371363</v>
+        <v>-1.028831318942252</v>
       </c>
       <c r="C24">
-        <v>0.566175495637442</v>
+        <v>-1.442321749770988</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.07293012713076806</v>
+        <v>1.042197215044069</v>
       </c>
       <c r="C25">
-        <v>1.759149195351716</v>
+        <v>-0.4308055936826986</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>2.382721244503041</v>
+        <v>2.249866129331338</v>
       </c>
       <c r="C26">
-        <v>-0.2428865688018846</v>
+        <v>-0.9199969368125862</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.808854003094632</v>
+        <v>-0.2908726717401174</v>
       </c>
       <c r="C27">
-        <v>2.156201122556989</v>
+        <v>0.6036249077193471</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.1705274982220134</v>
+        <v>-1.660181355753282</v>
       </c>
       <c r="C28">
-        <v>1.104288140129642</v>
+        <v>-0.8249691592443635</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.5634455808858522</v>
+        <v>0.3956942934212744</v>
       </c>
       <c r="C29">
-        <v>-0.3573600345267984</v>
+        <v>-0.03011907515616025</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.9321272995132753</v>
+        <v>-0.156728238367831</v>
       </c>
       <c r="C30">
-        <v>0.6791625601151263</v>
+        <v>-1.088879952479264</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.1651119286668924</v>
+        <v>1.430520802309561</v>
       </c>
       <c r="C31">
-        <v>-0.5065538577927541</v>
+        <v>-0.6861211512103342</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.8386480446191902</v>
+        <v>1.228119453469666</v>
       </c>
       <c r="C32">
-        <v>-1.886649026998763</v>
+        <v>1.283598955390457</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.3720002384698379</v>
+        <v>0.4227591877371565</v>
       </c>
       <c r="C33">
-        <v>-0.6901976399995219</v>
+        <v>-0.03047631508230159</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.4399641846388334</v>
+        <v>0.2865879323146154</v>
       </c>
       <c r="C34">
-        <v>-0.09214922366266279</v>
+        <v>-0.8772951277316814</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.2414605851923777</v>
+        <v>-0.3405044452978263</v>
       </c>
       <c r="C35">
-        <v>0.3588614218929461</v>
+        <v>0.0563315631981807</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.9108982443072113</v>
+        <v>-2.07502870299277</v>
       </c>
       <c r="C36">
-        <v>0.4955850807545769</v>
+        <v>2.100518153437314</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.4913033509204544</v>
+        <v>-0.8759996139498298</v>
       </c>
       <c r="C37">
-        <v>-0.5554558848924008</v>
+        <v>0.8911038749762338</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.1148488491562653</v>
+        <v>0.3887891817539884</v>
       </c>
       <c r="C38">
-        <v>0.3760925683498593</v>
+        <v>-0.6494653647224984</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.1618454841024817</v>
+        <v>-0.7434923840963257</v>
       </c>
       <c r="C39">
-        <v>0.9605938491877609</v>
+        <v>1.372705981528603</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-2.354442374719407</v>
+        <v>-1.255555588544158</v>
       </c>
       <c r="C40">
-        <v>1.643896722433538</v>
+        <v>0.9169840831797491</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.250490140105188</v>
+        <v>-0.8951644143285495</v>
       </c>
       <c r="C41">
-        <v>-1.166113545185336</v>
+        <v>1.122402406634922</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-1.442754720087236</v>
+        <v>-0.9692099638745705</v>
       </c>
       <c r="C42">
-        <v>1.01130120157072</v>
+        <v>0.3259638230901546</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.4300967373415498</v>
+        <v>1.288031586574001</v>
       </c>
       <c r="C43">
-        <v>-0.3986948325486567</v>
+        <v>-1.292509853309973</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-1.577715644654015</v>
+        <v>-1.406699621131697</v>
       </c>
       <c r="C44">
-        <v>0.05308942015160913</v>
+        <v>0.8343946521517328</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.02923529690276577</v>
+        <v>0.7038221120707797</v>
       </c>
       <c r="C45">
-        <v>-1.67391012315153</v>
+        <v>-1.141872872429911</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.236475449806448</v>
+        <v>2.713876944558021</v>
       </c>
       <c r="C46">
-        <v>-0.01816719032751698</v>
+        <v>-0.6980202637137136</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.5008113826403505</v>
+        <v>-0.1748637916887419</v>
       </c>
       <c r="C47">
-        <v>-0.779883647220714</v>
+        <v>-0.1153546851529035</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.5914734832297128</v>
+        <v>-0.2164587901027322</v>
       </c>
       <c r="C48">
-        <v>0.06868414305861649</v>
+        <v>0.1599063456640552</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>1.223430334303602</v>
+        <v>-2.279170532064995</v>
       </c>
       <c r="C49">
-        <v>-0.1582247756138286</v>
+        <v>-0.08243790579473942</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.1078309463311087</v>
+        <v>0.4195038708528956</v>
       </c>
       <c r="C50">
-        <v>1.120964921476417</v>
+        <v>1.238720604470399</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.957157183870911</v>
+        <v>-0.1773985888311386</v>
       </c>
       <c r="C51">
-        <v>-0.6954505821805421</v>
+        <v>-0.4881456203935171</v>
       </c>
     </row>
   </sheetData>
